--- a/docs/descargas/tasa_motociclistas_1000_motos_2024.xlsx
+++ b/docs/descargas/tasa_motociclistas_1000_motos_2024.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léeme" sheetId="1" r:id="R2652dfe794554c79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología" sheetId="2" r:id="Rb6b3c3dd0d4b4817"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2024" sheetId="3" r:id="R7d377f0f68b5485b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léeme" sheetId="1" r:id="R681bbc7fbd324023"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología" sheetId="2" r:id="R17c83af2eaec4bfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2024" sheetId="3" r:id="R013f688f87914a44"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -557,7 +557,7 @@
         <x:v>Producto</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>Descarga pública del Catálogo de datos del Observatorio REDSA</x:v>
+        <x:v>Descarga pública del Catálogo de datos del Observatorio de Seguridad Vial y Movilidad Sostenible</x:v>
       </x:c>
     </x:row>
     <x:row r="5">

--- a/docs/descargas/tasa_motociclistas_1000_motos_2024.xlsx
+++ b/docs/descargas/tasa_motociclistas_1000_motos_2024.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léeme" sheetId="1" r:id="R681bbc7fbd324023"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología" sheetId="2" r:id="R17c83af2eaec4bfc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2024" sheetId="3" r:id="R013f688f87914a44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léeme" sheetId="1" r:id="R82a4a51c3822461c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología" sheetId="2" r:id="R5d79be82c8b44e24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2024" sheetId="3" r:id="R0ee5dd16a7ba4ace"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -243,7 +243,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="56">
+  <x:cellXfs count="60">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -308,22 +308,34 @@
     <x:xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="6" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="6" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="6" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="7" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="7" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="7" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -613,7 +625,7 @@
         <x:v>Generado</x:v>
       </x:c>
       <x:c r="B11" s="9" t="str">
-        <x:v>2026-07-22</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -629,7 +641,7 @@
         <x:v>Cómo leer</x:v>
       </x:c>
       <x:c r="B13" s="9" t="str">
-        <x:v>Cada hoja anual presenta total nacional, subtotales provinciales y datos cantonales. Cuando existe nivel parroquial, incluye además subtotales cantonales y el detalle parroquial.</x:v>
+        <x:v>Cada hoja anual usa el nivel más detallado realmente disponible: parroquia cuando existe información comprobable para ese año; en caso contrario, cantón o provincia. Incluye subtotales y total nacional.</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -645,7 +657,7 @@
         <x:v>Citación sugerida</x:v>
       </x:c>
       <x:c r="B15" s="11" t="str">
-        <x:v>Fundación REDSA (2026). Motociclistas fallecidos por cada 1.000 motos (2024). Observatorio Ciudadano de Seguridad Vial y Movilidad Sostenible. Consulta: 2026-07-22.</x:v>
+        <x:v>Fundación REDSA (2026). Motociclistas fallecidos por cada 1.000 motos (2024). Observatorio Ciudadano de Seguridad Vial y Movilidad Sostenible. Consulta: 2026-07-27.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -773,6 +785,7 @@
     <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="55" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -789,6 +802,7 @@
       <x:c r="I1" s="2"/>
       <x:c r="J1" s="2"/>
       <x:c r="K1" s="2"/>
+      <x:c r="L1" s="2"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2"/>
@@ -802,6 +816,7 @@
       <x:c r="I2" s="2"/>
       <x:c r="J2" s="2"/>
       <x:c r="K2" s="2"/>
+      <x:c r="L2" s="2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="str">
@@ -817,6 +832,7 @@
       <x:c r="I3" s="12"/>
       <x:c r="J3" s="12"/>
       <x:c r="K3" s="12"/>
+      <x:c r="L3" s="12"/>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="33" t="str">
@@ -849,8 +865,11 @@
       <x:c r="J5" s="34" t="str">
         <x:v>Numerador</x:v>
       </x:c>
-      <x:c r="K5" s="35" t="str">
+      <x:c r="K5" s="34" t="str">
         <x:v>Denominador</x:v>
+      </x:c>
+      <x:c r="L5" s="35" t="str">
+        <x:v>Observación</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -874,9 +893,10 @@
       <x:c r="J6" s="39" t="n">
         <x:v>397</x:v>
       </x:c>
-      <x:c r="K6" s="40" t="n">
+      <x:c r="K6" s="39" t="n">
         <x:v>908770</x:v>
       </x:c>
+      <x:c r="L6" s="56" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="41" t="str">
@@ -901,9 +921,10 @@
       <x:c r="J7" s="44" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="K7" s="45" t="n">
+      <x:c r="K7" s="44" t="n">
         <x:v>26897</x:v>
       </x:c>
+      <x:c r="L7" s="57" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="46" t="str">
@@ -932,9 +953,10 @@
       <x:c r="J8" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K8" s="50" t="n">
+      <x:c r="K8" s="49" t="n">
         <x:v>2179</x:v>
       </x:c>
+      <x:c r="L8" s="58" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="46" t="str">
@@ -963,9 +985,10 @@
       <x:c r="J9" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K9" s="50" t="n">
+      <x:c r="K9" s="49" t="n">
         <x:v>439</x:v>
       </x:c>
+      <x:c r="L9" s="58" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="46" t="str">
@@ -994,9 +1017,10 @@
       <x:c r="J10" s="49" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="K10" s="50" t="n">
+      <x:c r="K10" s="49" t="n">
         <x:v>20480</x:v>
       </x:c>
+      <x:c r="L10" s="58" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="46" t="str">
@@ -1025,9 +1049,10 @@
       <x:c r="J11" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="50" t="n">
+      <x:c r="K11" s="49" t="n">
         <x:v>48</x:v>
       </x:c>
+      <x:c r="L11" s="58" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="46" t="str">
@@ -1056,9 +1081,10 @@
       <x:c r="J12" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="50" t="n">
+      <x:c r="K12" s="49" t="n">
         <x:v>248</x:v>
       </x:c>
+      <x:c r="L12" s="58" t="str"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="46" t="str">
@@ -1087,9 +1113,10 @@
       <x:c r="J13" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="50" t="n">
+      <x:c r="K13" s="49" t="n">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="L13" s="58" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="46" t="str">
@@ -1118,9 +1145,10 @@
       <x:c r="J14" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="50" t="n">
+      <x:c r="K14" s="49" t="n">
         <x:v>947</x:v>
       </x:c>
+      <x:c r="L14" s="58" t="str"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="46" t="str">
@@ -1149,9 +1177,10 @@
       <x:c r="J15" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="50" t="n">
+      <x:c r="K15" s="49" t="n">
         <x:v>143</x:v>
       </x:c>
+      <x:c r="L15" s="58" t="str"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="46" t="str">
@@ -1176,9 +1205,10 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J16" s="49"/>
-      <x:c r="K16" s="50" t="n">
+      <x:c r="K16" s="49" t="n">
         <x:v>149</x:v>
       </x:c>
+      <x:c r="L16" s="58" t="str"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="46" t="str">
@@ -1207,9 +1237,10 @@
       <x:c r="J17" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="50" t="n">
+      <x:c r="K17" s="49" t="n">
         <x:v>1865</x:v>
       </x:c>
+      <x:c r="L17" s="58" t="str"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="46" t="str">
@@ -1234,9 +1265,10 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J18" s="49"/>
-      <x:c r="K18" s="50" t="n">
+      <x:c r="K18" s="49" t="n">
         <x:v>399</x:v>
       </x:c>
+      <x:c r="L18" s="58" t="str"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="46" t="str">
@@ -1261,9 +1293,10 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J19" s="49"/>
-      <x:c r="K19" s="50" t="n">
+      <x:c r="K19" s="49" t="n">
         <x:v>45</x:v>
       </x:c>
+      <x:c r="L19" s="58" t="str"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="46" t="str">
@@ -1288,9 +1321,10 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J20" s="49"/>
-      <x:c r="K20" s="50" t="n">
+      <x:c r="K20" s="49" t="n">
         <x:v>970</x:v>
       </x:c>
+      <x:c r="L20" s="58" t="str"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="46" t="str">
@@ -1319,9 +1353,10 @@
       <x:c r="J21" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K21" s="50" t="n">
+      <x:c r="K21" s="49" t="n">
         <x:v>89</x:v>
       </x:c>
+      <x:c r="L21" s="58" t="str"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="46" t="str">
@@ -1350,9 +1385,10 @@
       <x:c r="J22" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="50" t="n">
+      <x:c r="K22" s="49" t="n">
         <x:v>364</x:v>
       </x:c>
+      <x:c r="L22" s="58" t="str"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="41" t="str">
@@ -1377,9 +1413,10 @@
       <x:c r="J23" s="44" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="K23" s="45" t="n">
+      <x:c r="K23" s="44" t="n">
         <x:v>11733</x:v>
       </x:c>
+      <x:c r="L23" s="57" t="str"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="46" t="str">
@@ -1408,9 +1445,10 @@
       <x:c r="J24" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="50" t="n">
+      <x:c r="K24" s="49" t="n">
         <x:v>2450</x:v>
       </x:c>
+      <x:c r="L24" s="58" t="str"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="46" t="str">
@@ -1439,9 +1477,10 @@
       <x:c r="J25" s="49" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K25" s="50" t="n">
+      <x:c r="K25" s="49" t="n">
         <x:v>869</x:v>
       </x:c>
+      <x:c r="L25" s="58" t="str"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="46" t="str">
@@ -1470,9 +1509,10 @@
       <x:c r="J26" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K26" s="50" t="n">
+      <x:c r="K26" s="49" t="n">
         <x:v>688</x:v>
       </x:c>
+      <x:c r="L26" s="58" t="str"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="46" t="str">
@@ -1501,9 +1541,10 @@
       <x:c r="J27" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="50" t="n">
+      <x:c r="K27" s="49" t="n">
         <x:v>1809</x:v>
       </x:c>
+      <x:c r="L27" s="58" t="str"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="46" t="str">
@@ -1532,9 +1573,10 @@
       <x:c r="J28" s="49" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K28" s="50" t="n">
+      <x:c r="K28" s="49" t="n">
         <x:v>3132</x:v>
       </x:c>
+      <x:c r="L28" s="58" t="str"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="46" t="str">
@@ -1563,9 +1605,10 @@
       <x:c r="J29" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K29" s="50" t="n">
+      <x:c r="K29" s="49" t="n">
         <x:v>1352</x:v>
       </x:c>
+      <x:c r="L29" s="58" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="46" t="str">
@@ -1594,9 +1637,10 @@
       <x:c r="J30" s="49" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K30" s="50" t="n">
+      <x:c r="K30" s="49" t="n">
         <x:v>1433</x:v>
       </x:c>
+      <x:c r="L30" s="58" t="str"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="41" t="str">
@@ -1621,9 +1665,10 @@
       <x:c r="J31" s="44" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K31" s="45" t="n">
+      <x:c r="K31" s="44" t="n">
         <x:v>11765</x:v>
       </x:c>
+      <x:c r="L31" s="57" t="str"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="46" t="str">
@@ -1652,9 +1697,10 @@
       <x:c r="J32" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="50" t="n">
+      <x:c r="K32" s="49" t="n">
         <x:v>2215</x:v>
       </x:c>
+      <x:c r="L32" s="58" t="str"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="46" t="str">
@@ -1683,9 +1729,10 @@
       <x:c r="J33" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="50" t="n">
+      <x:c r="K33" s="49" t="n">
         <x:v>326</x:v>
       </x:c>
+      <x:c r="L33" s="58" t="str"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="46" t="str">
@@ -1714,9 +1761,10 @@
       <x:c r="J34" s="49" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K34" s="50" t="n">
+      <x:c r="K34" s="49" t="n">
         <x:v>975</x:v>
       </x:c>
+      <x:c r="L34" s="58" t="str"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="46" t="str">
@@ -1741,9 +1789,10 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J35" s="49"/>
-      <x:c r="K35" s="50" t="n">
+      <x:c r="K35" s="49" t="n">
         <x:v>222</x:v>
       </x:c>
+      <x:c r="L35" s="58" t="str"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="46" t="str">
@@ -1772,9 +1821,10 @@
       <x:c r="J36" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K36" s="50" t="n">
+      <x:c r="K36" s="49" t="n">
         <x:v>124</x:v>
       </x:c>
+      <x:c r="L36" s="58" t="str"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="46" t="str">
@@ -1803,9 +1853,10 @@
       <x:c r="J37" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K37" s="50" t="n">
+      <x:c r="K37" s="49" t="n">
         <x:v>8046</x:v>
       </x:c>
+      <x:c r="L37" s="58" t="str"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="46" t="str">
@@ -1834,9 +1885,10 @@
       <x:c r="J38" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K38" s="50" t="n">
+      <x:c r="K38" s="49" t="n">
         <x:v>79</x:v>
       </x:c>
+      <x:c r="L38" s="58" t="str"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="41" t="str">
@@ -1861,9 +1913,10 @@
       <x:c r="J39" s="44" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K39" s="45" t="n">
+      <x:c r="K39" s="44" t="n">
         <x:v>3476</x:v>
       </x:c>
+      <x:c r="L39" s="57" t="str"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="46" t="str">
@@ -1892,9 +1945,10 @@
       <x:c r="J40" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K40" s="50" t="n">
+      <x:c r="K40" s="49" t="n">
         <x:v>259</x:v>
       </x:c>
+      <x:c r="L40" s="58" t="str"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="46" t="str">
@@ -1923,9 +1977,10 @@
       <x:c r="J41" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K41" s="50" t="n">
+      <x:c r="K41" s="49" t="n">
         <x:v>282</x:v>
       </x:c>
+      <x:c r="L41" s="58" t="str"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="46" t="str">
@@ -1954,9 +2009,10 @@
       <x:c r="J42" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K42" s="50" t="n">
+      <x:c r="K42" s="49" t="n">
         <x:v>273</x:v>
       </x:c>
+      <x:c r="L42" s="58" t="str"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="46" t="str">
@@ -1985,9 +2041,10 @@
       <x:c r="J43" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K43" s="50" t="n">
+      <x:c r="K43" s="49" t="n">
         <x:v>621</x:v>
       </x:c>
+      <x:c r="L43" s="58" t="str"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="46" t="str">
@@ -2016,9 +2073,10 @@
       <x:c r="J44" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K44" s="50" t="n">
+      <x:c r="K44" s="49" t="n">
         <x:v>125</x:v>
       </x:c>
+      <x:c r="L44" s="58" t="str"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="46" t="str">
@@ -2047,9 +2105,10 @@
       <x:c r="J45" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K45" s="50" t="n">
+      <x:c r="K45" s="49" t="n">
         <x:v>1916</x:v>
       </x:c>
+      <x:c r="L45" s="58" t="str"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="41" t="str">
@@ -2074,9 +2133,10 @@
       <x:c r="J46" s="44" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="K46" s="45" t="n">
+      <x:c r="K46" s="44" t="n">
         <x:v>11288</x:v>
       </x:c>
+      <x:c r="L46" s="57" t="str"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="46" t="str">
@@ -2105,9 +2165,10 @@
       <x:c r="J47" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K47" s="50" t="n">
+      <x:c r="K47" s="49" t="n">
         <x:v>351</x:v>
       </x:c>
+      <x:c r="L47" s="58" t="str"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="46" t="str">
@@ -2136,9 +2197,10 @@
       <x:c r="J48" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K48" s="50" t="n">
+      <x:c r="K48" s="49" t="n">
         <x:v>169</x:v>
       </x:c>
+      <x:c r="L48" s="58" t="str"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="46" t="str">
@@ -2167,9 +2229,10 @@
       <x:c r="J49" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K49" s="50" t="n">
+      <x:c r="K49" s="49" t="n">
         <x:v>224</x:v>
       </x:c>
+      <x:c r="L49" s="58" t="str"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="46" t="str">
@@ -2198,9 +2261,10 @@
       <x:c r="J50" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K50" s="50" t="n">
+      <x:c r="K50" s="49" t="n">
         <x:v>147</x:v>
       </x:c>
+      <x:c r="L50" s="58" t="str"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="46" t="str">
@@ -2229,9 +2293,10 @@
       <x:c r="J51" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K51" s="50" t="n">
+      <x:c r="K51" s="49" t="n">
         <x:v>858</x:v>
       </x:c>
+      <x:c r="L51" s="58" t="str"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="46" t="str">
@@ -2260,9 +2325,10 @@
       <x:c r="J52" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K52" s="50" t="n">
+      <x:c r="K52" s="49" t="n">
         <x:v>193</x:v>
       </x:c>
+      <x:c r="L52" s="58" t="str"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="46" t="str">
@@ -2291,9 +2357,10 @@
       <x:c r="J53" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K53" s="50" t="n">
+      <x:c r="K53" s="49" t="n">
         <x:v>617</x:v>
       </x:c>
+      <x:c r="L53" s="58" t="str"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="46" t="str">
@@ -2322,9 +2389,10 @@
       <x:c r="J54" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K54" s="50" t="n">
+      <x:c r="K54" s="49" t="n">
         <x:v>438</x:v>
       </x:c>
+      <x:c r="L54" s="58" t="str"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="46" t="str">
@@ -2353,9 +2421,10 @@
       <x:c r="J55" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K55" s="50" t="n">
+      <x:c r="K55" s="49" t="n">
         <x:v>265</x:v>
       </x:c>
+      <x:c r="L55" s="58" t="str"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="46" t="str">
@@ -2384,9 +2453,10 @@
       <x:c r="J56" s="49" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K56" s="50" t="n">
+      <x:c r="K56" s="49" t="n">
         <x:v>8026</x:v>
       </x:c>
+      <x:c r="L56" s="58" t="str"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="41" t="str">
@@ -2411,9 +2481,10 @@
       <x:c r="J57" s="44" t="n">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="K57" s="45" t="n">
+      <x:c r="K57" s="44" t="n">
         <x:v>16260</x:v>
       </x:c>
+      <x:c r="L57" s="57" t="str"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="46" t="str">
@@ -2442,9 +2513,10 @@
       <x:c r="J58" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K58" s="50" t="n">
+      <x:c r="K58" s="49" t="n">
         <x:v>6698</x:v>
       </x:c>
+      <x:c r="L58" s="58" t="str"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="46" t="str">
@@ -2473,9 +2545,10 @@
       <x:c r="J59" s="49" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="K59" s="50" t="n">
+      <x:c r="K59" s="49" t="n">
         <x:v>4449</x:v>
       </x:c>
+      <x:c r="L59" s="58" t="str"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="46" t="str">
@@ -2504,9 +2577,10 @@
       <x:c r="J60" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K60" s="50" t="n">
+      <x:c r="K60" s="49" t="n">
         <x:v>1692</x:v>
       </x:c>
+      <x:c r="L60" s="58" t="str"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="46" t="str">
@@ -2535,9 +2609,10 @@
       <x:c r="J61" s="49" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K61" s="50" t="n">
+      <x:c r="K61" s="49" t="n">
         <x:v>1100</x:v>
       </x:c>
+      <x:c r="L61" s="58" t="str"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="46" t="str">
@@ -2566,9 +2641,10 @@
       <x:c r="J62" s="49" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K62" s="50" t="n">
+      <x:c r="K62" s="49" t="n">
         <x:v>1953</x:v>
       </x:c>
+      <x:c r="L62" s="58" t="str"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="46" t="str">
@@ -2593,9 +2669,10 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J63" s="49"/>
-      <x:c r="K63" s="50" t="n">
+      <x:c r="K63" s="49" t="n">
         <x:v>190</x:v>
       </x:c>
+      <x:c r="L63" s="58" t="str"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="46" t="str">
@@ -2624,9 +2701,10 @@
       <x:c r="J64" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K64" s="50" t="n">
+      <x:c r="K64" s="49" t="n">
         <x:v>368</x:v>
       </x:c>
+      <x:c r="L64" s="58" t="str"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="41" t="str">
@@ -2651,9 +2729,10 @@
       <x:c r="J65" s="44" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K65" s="45" t="n">
+      <x:c r="K65" s="44" t="n">
         <x:v>56802</x:v>
       </x:c>
+      <x:c r="L65" s="57" t="str"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="46" t="str">
@@ -2682,9 +2761,10 @@
       <x:c r="J66" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K66" s="50" t="n">
+      <x:c r="K66" s="49" t="n">
         <x:v>3680</x:v>
       </x:c>
+      <x:c r="L66" s="58" t="str"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="46" t="str">
@@ -2709,9 +2789,10 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J67" s="49"/>
-      <x:c r="K67" s="50" t="n">
+      <x:c r="K67" s="49" t="n">
         <x:v>465</x:v>
       </x:c>
+      <x:c r="L67" s="58" t="str"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="46" t="str">
@@ -2740,9 +2821,10 @@
       <x:c r="J68" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K68" s="50" t="n">
+      <x:c r="K68" s="49" t="n">
         <x:v>721</x:v>
       </x:c>
+      <x:c r="L68" s="58" t="str"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="46" t="str">
@@ -2767,9 +2849,10 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J69" s="49"/>
-      <x:c r="K69" s="50" t="n">
+      <x:c r="K69" s="49" t="n">
         <x:v>106</x:v>
       </x:c>
+      <x:c r="L69" s="58" t="str"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="46" t="str">
@@ -2798,9 +2881,10 @@
       <x:c r="J70" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K70" s="50" t="n">
+      <x:c r="K70" s="49" t="n">
         <x:v>4434</x:v>
       </x:c>
+      <x:c r="L70" s="58" t="str"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="46" t="str">
@@ -2829,9 +2913,10 @@
       <x:c r="J71" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K71" s="50" t="n">
+      <x:c r="K71" s="49" t="n">
         <x:v>7008</x:v>
       </x:c>
+      <x:c r="L71" s="58" t="str"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="46" t="str">
@@ -2860,9 +2945,10 @@
       <x:c r="J72" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K72" s="50" t="n">
+      <x:c r="K72" s="49" t="n">
         <x:v>551</x:v>
       </x:c>
+      <x:c r="L72" s="58" t="str"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="46" t="str">
@@ -2891,9 +2977,10 @@
       <x:c r="J73" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K73" s="50" t="n">
+      <x:c r="K73" s="49" t="n">
         <x:v>20838</x:v>
       </x:c>
+      <x:c r="L73" s="58" t="str"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="46" t="str">
@@ -2918,9 +3005,10 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J74" s="49"/>
-      <x:c r="K74" s="50" t="n">
+      <x:c r="K74" s="49" t="n">
         <x:v>1027</x:v>
       </x:c>
+      <x:c r="L74" s="58" t="str"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="46" t="str">
@@ -2949,9 +3037,10 @@
       <x:c r="J75" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K75" s="50" t="n">
+      <x:c r="K75" s="49" t="n">
         <x:v>9078</x:v>
       </x:c>
+      <x:c r="L75" s="58" t="str"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="46" t="str">
@@ -2980,9 +3069,10 @@
       <x:c r="J76" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K76" s="50" t="n">
+      <x:c r="K76" s="49" t="n">
         <x:v>1976</x:v>
       </x:c>
+      <x:c r="L76" s="58" t="str"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="46" t="str">
@@ -3011,9 +3101,10 @@
       <x:c r="J77" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K77" s="50" t="n">
+      <x:c r="K77" s="49" t="n">
         <x:v>956</x:v>
       </x:c>
+      <x:c r="L77" s="58" t="str"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="46" t="str">
@@ -3042,9 +3133,10 @@
       <x:c r="J78" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K78" s="50" t="n">
+      <x:c r="K78" s="49" t="n">
         <x:v>6040</x:v>
       </x:c>
+      <x:c r="L78" s="58" t="str"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="46" t="str">
@@ -3073,9 +3165,10 @@
       <x:c r="J79" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K79" s="50" t="n">
+      <x:c r="K79" s="49" t="n">
         <x:v>1520</x:v>
       </x:c>
+      <x:c r="L79" s="58" t="str"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="41" t="str">
@@ -3100,9 +3193,10 @@
       <x:c r="J80" s="44" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K80" s="45" t="n">
+      <x:c r="K80" s="44" t="n">
         <x:v>26174</x:v>
       </x:c>
+      <x:c r="L80" s="57" t="str"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="46" t="str">
@@ -3131,9 +3225,10 @@
       <x:c r="J81" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K81" s="50" t="n">
+      <x:c r="K81" s="49" t="n">
         <x:v>2890</x:v>
       </x:c>
+      <x:c r="L81" s="58" t="str"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="46" t="str">
@@ -3162,9 +3257,10 @@
       <x:c r="J82" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K82" s="50" t="n">
+      <x:c r="K82" s="49" t="n">
         <x:v>444</x:v>
       </x:c>
+      <x:c r="L82" s="58" t="str"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="46" t="str">
@@ -3193,9 +3289,10 @@
       <x:c r="J83" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K83" s="50" t="n">
+      <x:c r="K83" s="49" t="n">
         <x:v>9839</x:v>
       </x:c>
+      <x:c r="L83" s="58" t="str"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="46" t="str">
@@ -3224,9 +3321,10 @@
       <x:c r="J84" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K84" s="50" t="n">
+      <x:c r="K84" s="49" t="n">
         <x:v>974</x:v>
       </x:c>
+      <x:c r="L84" s="58" t="str"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="46" t="str">
@@ -3255,9 +3353,10 @@
       <x:c r="J85" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K85" s="50" t="n">
+      <x:c r="K85" s="49" t="n">
         <x:v>11055</x:v>
       </x:c>
+      <x:c r="L85" s="58" t="str"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="46" t="str">
@@ -3286,9 +3385,10 @@
       <x:c r="J86" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K86" s="50" t="n">
+      <x:c r="K86" s="49" t="n">
         <x:v>342</x:v>
       </x:c>
+      <x:c r="L86" s="58" t="str"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="46" t="str">
@@ -3317,9 +3417,10 @@
       <x:c r="J87" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K87" s="50" t="n">
+      <x:c r="K87" s="49" t="n">
         <x:v>630</x:v>
       </x:c>
+      <x:c r="L87" s="58" t="str"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="41" t="str">
@@ -3344,9 +3445,10 @@
       <x:c r="J88" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K88" s="45" t="n">
+      <x:c r="K88" s="44" t="n">
         <x:v>1859</x:v>
       </x:c>
+      <x:c r="L88" s="57" t="str"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="46" t="str">
@@ -3371,9 +3473,10 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J89" s="49"/>
-      <x:c r="K89" s="50" t="n">
+      <x:c r="K89" s="49" t="n">
         <x:v>64</x:v>
       </x:c>
+      <x:c r="L89" s="58" t="str"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="46" t="str">
@@ -3402,9 +3505,10 @@
       <x:c r="J90" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K90" s="50" t="n">
+      <x:c r="K90" s="49" t="n">
         <x:v>748</x:v>
       </x:c>
+      <x:c r="L90" s="58" t="str"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="46" t="str">
@@ -3433,9 +3537,10 @@
       <x:c r="J91" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K91" s="50" t="n">
+      <x:c r="K91" s="49" t="n">
         <x:v>1111</x:v>
       </x:c>
+      <x:c r="L91" s="58" t="str"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="41" t="str">
@@ -3460,9 +3565,10 @@
       <x:c r="J92" s="44" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K92" s="45" t="n">
+      <x:c r="K92" s="44" t="n">
         <x:v>251968</x:v>
       </x:c>
+      <x:c r="L92" s="57" t="str"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="46" t="str">
@@ -3491,9 +3597,10 @@
       <x:c r="J93" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K93" s="50" t="n">
+      <x:c r="K93" s="49" t="n">
         <x:v>1280</x:v>
       </x:c>
+      <x:c r="L93" s="58" t="str"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="46" t="str">
@@ -3522,9 +3629,10 @@
       <x:c r="J94" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K94" s="50" t="n">
+      <x:c r="K94" s="49" t="n">
         <x:v>702</x:v>
       </x:c>
+      <x:c r="L94" s="58" t="str"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="46" t="str">
@@ -3553,9 +3661,10 @@
       <x:c r="J95" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K95" s="50" t="n">
+      <x:c r="K95" s="49" t="n">
         <x:v>6369</x:v>
       </x:c>
+      <x:c r="L95" s="58" t="str"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="46" t="str">
@@ -3584,9 +3693,10 @@
       <x:c r="J96" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K96" s="50" t="n">
+      <x:c r="K96" s="49" t="n">
         <x:v>1272</x:v>
       </x:c>
+      <x:c r="L96" s="58" t="str"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="46" t="str">
@@ -3615,9 +3725,10 @@
       <x:c r="J97" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K97" s="50" t="n">
+      <x:c r="K97" s="49" t="n">
         <x:v>682</x:v>
       </x:c>
+      <x:c r="L97" s="58" t="str"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="46" t="str">
@@ -3646,9 +3757,10 @@
       <x:c r="J98" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K98" s="50" t="n">
+      <x:c r="K98" s="49" t="n">
         <x:v>9174</x:v>
       </x:c>
+      <x:c r="L98" s="58" t="str"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="46" t="str">
@@ -3677,9 +3789,10 @@
       <x:c r="J99" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K99" s="50" t="n">
+      <x:c r="K99" s="49" t="n">
         <x:v>8678</x:v>
       </x:c>
+      <x:c r="L99" s="58" t="str"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="46" t="str">
@@ -3708,9 +3821,10 @@
       <x:c r="J100" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K100" s="50" t="n">
+      <x:c r="K100" s="49" t="n">
         <x:v>6863</x:v>
       </x:c>
+      <x:c r="L100" s="58" t="str"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="46" t="str">
@@ -3739,9 +3853,10 @@
       <x:c r="J101" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K101" s="50" t="n">
+      <x:c r="K101" s="49" t="n">
         <x:v>5215</x:v>
       </x:c>
+      <x:c r="L101" s="58" t="str"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="46" t="str">
@@ -3770,9 +3885,10 @@
       <x:c r="J102" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K102" s="50" t="n">
+      <x:c r="K102" s="49" t="n">
         <x:v>17229</x:v>
       </x:c>
+      <x:c r="L102" s="58" t="str"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="46" t="str">
@@ -3801,9 +3917,10 @@
       <x:c r="J103" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K103" s="50" t="n">
+      <x:c r="K103" s="49" t="n">
         <x:v>132932</x:v>
       </x:c>
+      <x:c r="L103" s="58" t="str"/>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="46" t="str">
@@ -3832,9 +3949,10 @@
       <x:c r="J104" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K104" s="50" t="n">
+      <x:c r="K104" s="49" t="n">
         <x:v>1156</x:v>
       </x:c>
+      <x:c r="L104" s="58" t="str"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="46" t="str">
@@ -3863,9 +3981,10 @@
       <x:c r="J105" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K105" s="50" t="n">
+      <x:c r="K105" s="49" t="n">
         <x:v>1287</x:v>
       </x:c>
+      <x:c r="L105" s="58" t="str"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="46" t="str">
@@ -3894,9 +4013,10 @@
       <x:c r="J106" s="49" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K106" s="50" t="n">
+      <x:c r="K106" s="49" t="n">
         <x:v>19904</x:v>
       </x:c>
+      <x:c r="L106" s="58" t="str"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="46" t="str">
@@ -3925,9 +4045,10 @@
       <x:c r="J107" s="49" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="K107" s="50" t="n">
+      <x:c r="K107" s="49" t="n">
         <x:v>8572</x:v>
       </x:c>
+      <x:c r="L107" s="58" t="str"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="46" t="str">
@@ -3956,9 +4077,10 @@
       <x:c r="J108" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K108" s="50" t="n">
+      <x:c r="K108" s="49" t="n">
         <x:v>8858</x:v>
       </x:c>
+      <x:c r="L108" s="58" t="str"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="46" t="str">
@@ -3987,9 +4109,10 @@
       <x:c r="J109" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K109" s="50" t="n">
+      <x:c r="K109" s="49" t="n">
         <x:v>1556</x:v>
       </x:c>
+      <x:c r="L109" s="58" t="str"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="46" t="str">
@@ -4018,9 +4141,10 @@
       <x:c r="J110" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K110" s="50" t="n">
+      <x:c r="K110" s="49" t="n">
         <x:v>867</x:v>
       </x:c>
+      <x:c r="L110" s="58" t="str"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="46" t="str">
@@ -4049,9 +4173,10 @@
       <x:c r="J111" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K111" s="50" t="n">
+      <x:c r="K111" s="49" t="n">
         <x:v>2801</x:v>
       </x:c>
+      <x:c r="L111" s="58" t="str"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="46" t="str">
@@ -4080,9 +4205,10 @@
       <x:c r="J112" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K112" s="50" t="n">
+      <x:c r="K112" s="49" t="n">
         <x:v>3496</x:v>
       </x:c>
+      <x:c r="L112" s="58" t="str"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="46" t="str">
@@ -4111,9 +4237,10 @@
       <x:c r="J113" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K113" s="50" t="n">
+      <x:c r="K113" s="49" t="n">
         <x:v>4437</x:v>
       </x:c>
+      <x:c r="L113" s="58" t="str"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="46" t="str">
@@ -4142,9 +4269,10 @@
       <x:c r="J114" s="49" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K114" s="50" t="n">
+      <x:c r="K114" s="49" t="n">
         <x:v>1981</x:v>
       </x:c>
+      <x:c r="L114" s="58" t="str"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="46" t="str">
@@ -4173,9 +4301,10 @@
       <x:c r="J115" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K115" s="50" t="n">
+      <x:c r="K115" s="49" t="n">
         <x:v>2250</x:v>
       </x:c>
+      <x:c r="L115" s="58" t="str"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="46" t="str">
@@ -4204,9 +4333,10 @@
       <x:c r="J116" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K116" s="50" t="n">
+      <x:c r="K116" s="49" t="n">
         <x:v>2501</x:v>
       </x:c>
+      <x:c r="L116" s="58" t="str"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="46" t="str">
@@ -4235,9 +4365,10 @@
       <x:c r="J117" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K117" s="50" t="n">
+      <x:c r="K117" s="49" t="n">
         <x:v>1906</x:v>
       </x:c>
+      <x:c r="L117" s="58" t="str"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="41" t="str">
@@ -4262,9 +4393,10 @@
       <x:c r="J118" s="44" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K118" s="45" t="n">
+      <x:c r="K118" s="44" t="n">
         <x:v>14268</x:v>
       </x:c>
+      <x:c r="L118" s="57" t="str"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="46" t="str">
@@ -4293,9 +4425,10 @@
       <x:c r="J119" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K119" s="50" t="n">
+      <x:c r="K119" s="49" t="n">
         <x:v>1199</x:v>
       </x:c>
+      <x:c r="L119" s="58" t="str"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="46" t="str">
@@ -4324,9 +4457,10 @@
       <x:c r="J120" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K120" s="50" t="n">
+      <x:c r="K120" s="49" t="n">
         <x:v>1247</x:v>
       </x:c>
+      <x:c r="L120" s="58" t="str"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="46" t="str">
@@ -4355,9 +4489,10 @@
       <x:c r="J121" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K121" s="50" t="n">
+      <x:c r="K121" s="49" t="n">
         <x:v>9084</x:v>
       </x:c>
+      <x:c r="L121" s="58" t="str"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="46" t="str">
@@ -4386,9 +4521,10 @@
       <x:c r="J122" s="49" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K122" s="50" t="n">
+      <x:c r="K122" s="49" t="n">
         <x:v>1847</x:v>
       </x:c>
+      <x:c r="L122" s="58" t="str"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="46" t="str">
@@ -4417,9 +4553,10 @@
       <x:c r="J123" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K123" s="50" t="n">
+      <x:c r="K123" s="49" t="n">
         <x:v>334</x:v>
       </x:c>
+      <x:c r="L123" s="58" t="str"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="46" t="str">
@@ -4448,9 +4585,10 @@
       <x:c r="J124" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K124" s="50" t="n">
+      <x:c r="K124" s="49" t="n">
         <x:v>557</x:v>
       </x:c>
+      <x:c r="L124" s="58" t="str"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="41" t="str">
@@ -4471,7 +4609,8 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J125" s="44"/>
-      <x:c r="K125" s="45"/>
+      <x:c r="K125" s="44"/>
+      <x:c r="L125" s="57" t="str"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="46" t="str">
@@ -4496,7 +4635,8 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J126" s="49"/>
-      <x:c r="K126" s="50"/>
+      <x:c r="K126" s="49"/>
+      <x:c r="L126" s="58" t="str"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="41" t="str">
@@ -4521,9 +4661,10 @@
       <x:c r="J127" s="44" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K127" s="45" t="n">
+      <x:c r="K127" s="44" t="n">
         <x:v>14824</x:v>
       </x:c>
+      <x:c r="L127" s="57" t="str"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="46" t="str">
@@ -4552,9 +4693,10 @@
       <x:c r="J128" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K128" s="50" t="n">
+      <x:c r="K128" s="49" t="n">
         <x:v>710</x:v>
       </x:c>
+      <x:c r="L128" s="58" t="str"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="46" t="str">
@@ -4583,9 +4725,10 @@
       <x:c r="J129" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K129" s="50" t="n">
+      <x:c r="K129" s="49" t="n">
         <x:v>1004</x:v>
       </x:c>
+      <x:c r="L129" s="58" t="str"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="46" t="str">
@@ -4614,9 +4757,10 @@
       <x:c r="J130" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K130" s="50" t="n">
+      <x:c r="K130" s="49" t="n">
         <x:v>670</x:v>
       </x:c>
+      <x:c r="L130" s="58" t="str"/>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="46" t="str">
@@ -4645,9 +4789,10 @@
       <x:c r="J131" s="49" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K131" s="50" t="n">
+      <x:c r="K131" s="49" t="n">
         <x:v>239</x:v>
       </x:c>
+      <x:c r="L131" s="58" t="str"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="46" t="str">
@@ -4672,9 +4817,10 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J132" s="49"/>
-      <x:c r="K132" s="50" t="n">
+      <x:c r="K132" s="49" t="n">
         <x:v>423</x:v>
       </x:c>
+      <x:c r="L132" s="58" t="str"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="46" t="str">
@@ -4703,9 +4849,10 @@
       <x:c r="J133" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K133" s="50" t="n">
+      <x:c r="K133" s="49" t="n">
         <x:v>230</x:v>
       </x:c>
+      <x:c r="L133" s="58" t="str"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="46" t="str">
@@ -4734,9 +4881,10 @@
       <x:c r="J134" s="49" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="K134" s="50" t="n">
+      <x:c r="K134" s="49" t="n">
         <x:v>6889</x:v>
       </x:c>
+      <x:c r="L134" s="58" t="str"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="46" t="str">
@@ -4765,9 +4913,10 @@
       <x:c r="J135" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K135" s="50" t="n">
+      <x:c r="K135" s="49" t="n">
         <x:v>1565</x:v>
       </x:c>
+      <x:c r="L135" s="58" t="str"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="46" t="str">
@@ -4796,9 +4945,10 @@
       <x:c r="J136" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K136" s="50" t="n">
+      <x:c r="K136" s="49" t="n">
         <x:v>80</x:v>
       </x:c>
+      <x:c r="L136" s="58" t="str"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="46" t="str">
@@ -4827,9 +4977,10 @@
       <x:c r="J137" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K137" s="50" t="n">
+      <x:c r="K137" s="49" t="n">
         <x:v>469</x:v>
       </x:c>
+      <x:c r="L137" s="58" t="str"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="46" t="str">
@@ -4858,9 +5009,10 @@
       <x:c r="J138" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K138" s="50" t="n">
+      <x:c r="K138" s="49" t="n">
         <x:v>720</x:v>
       </x:c>
+      <x:c r="L138" s="58" t="str"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="46" t="str">
@@ -4889,9 +5041,10 @@
       <x:c r="J139" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K139" s="50" t="n">
+      <x:c r="K139" s="49" t="n">
         <x:v>849</x:v>
       </x:c>
+      <x:c r="L139" s="58" t="str"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="46" t="str">
@@ -4916,9 +5069,10 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J140" s="49"/>
-      <x:c r="K140" s="50" t="n">
+      <x:c r="K140" s="49" t="n">
         <x:v>82</x:v>
       </x:c>
+      <x:c r="L140" s="58" t="str"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="46" t="str">
@@ -4947,9 +5101,10 @@
       <x:c r="J141" s="49" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K141" s="50" t="n">
+      <x:c r="K141" s="49" t="n">
         <x:v>484</x:v>
       </x:c>
+      <x:c r="L141" s="58" t="str"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="46" t="str">
@@ -4974,9 +5129,10 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J142" s="49"/>
-      <x:c r="K142" s="50" t="n">
+      <x:c r="K142" s="49" t="n">
         <x:v>134</x:v>
       </x:c>
+      <x:c r="L142" s="58" t="str"/>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="46" t="str">
@@ -5005,9 +5161,10 @@
       <x:c r="J143" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K143" s="50" t="n">
+      <x:c r="K143" s="49" t="n">
         <x:v>915</x:v>
       </x:c>
+      <x:c r="L143" s="58" t="str"/>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="41" t="str">
@@ -5032,9 +5189,10 @@
       <x:c r="J144" s="44" t="n">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="K144" s="45" t="n">
+      <x:c r="K144" s="44" t="n">
         <x:v>89238</x:v>
       </x:c>
+      <x:c r="L144" s="57" t="str"/>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="46" t="str">
@@ -5063,9 +5221,10 @@
       <x:c r="J145" s="49" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K145" s="50" t="n">
+      <x:c r="K145" s="49" t="n">
         <x:v>3563</x:v>
       </x:c>
+      <x:c r="L145" s="58" t="str"/>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="46" t="str">
@@ -5094,9 +5253,10 @@
       <x:c r="J146" s="49" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="K146" s="50" t="n">
+      <x:c r="K146" s="49" t="n">
         <x:v>20511</x:v>
       </x:c>
+      <x:c r="L146" s="58" t="str"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="46" t="str">
@@ -5125,9 +5285,10 @@
       <x:c r="J147" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K147" s="50" t="n">
+      <x:c r="K147" s="49" t="n">
         <x:v>7864</x:v>
       </x:c>
+      <x:c r="L147" s="58" t="str"/>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="46" t="str">
@@ -5156,9 +5317,10 @@
       <x:c r="J148" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K148" s="50" t="n">
+      <x:c r="K148" s="49" t="n">
         <x:v>4899</x:v>
       </x:c>
+      <x:c r="L148" s="58" t="str"/>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="46" t="str">
@@ -5187,9 +5349,10 @@
       <x:c r="J149" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K149" s="50" t="n">
+      <x:c r="K149" s="49" t="n">
         <x:v>3650</x:v>
       </x:c>
+      <x:c r="L149" s="58" t="str"/>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="46" t="str">
@@ -5218,9 +5381,10 @@
       <x:c r="J150" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K150" s="50" t="n">
+      <x:c r="K150" s="49" t="n">
         <x:v>1665</x:v>
       </x:c>
+      <x:c r="L150" s="58" t="str"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="46" t="str">
@@ -5249,9 +5413,10 @@
       <x:c r="J151" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K151" s="50" t="n">
+      <x:c r="K151" s="49" t="n">
         <x:v>3043</x:v>
       </x:c>
+      <x:c r="L151" s="58" t="str"/>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="46" t="str">
@@ -5280,9 +5445,10 @@
       <x:c r="J152" s="49" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K152" s="50" t="n">
+      <x:c r="K152" s="49" t="n">
         <x:v>17948</x:v>
       </x:c>
+      <x:c r="L152" s="58" t="str"/>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="46" t="str">
@@ -5311,9 +5477,10 @@
       <x:c r="J153" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K153" s="50" t="n">
+      <x:c r="K153" s="49" t="n">
         <x:v>3210</x:v>
       </x:c>
+      <x:c r="L153" s="58" t="str"/>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="46" t="str">
@@ -5342,9 +5509,10 @@
       <x:c r="J154" s="49" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K154" s="50" t="n">
+      <x:c r="K154" s="49" t="n">
         <x:v>2509</x:v>
       </x:c>
+      <x:c r="L154" s="58" t="str"/>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="46" t="str">
@@ -5373,9 +5541,10 @@
       <x:c r="J155" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K155" s="50" t="n">
+      <x:c r="K155" s="49" t="n">
         <x:v>3804</x:v>
       </x:c>
+      <x:c r="L155" s="58" t="str"/>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="46" t="str">
@@ -5404,9 +5573,10 @@
       <x:c r="J156" s="49" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K156" s="50" t="n">
+      <x:c r="K156" s="49" t="n">
         <x:v>6725</x:v>
       </x:c>
+      <x:c r="L156" s="58" t="str"/>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="46" t="str">
@@ -5435,9 +5605,10 @@
       <x:c r="J157" s="49" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K157" s="50" t="n">
+      <x:c r="K157" s="49" t="n">
         <x:v>9847</x:v>
       </x:c>
+      <x:c r="L157" s="58" t="str"/>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="41" t="str">
@@ -5462,9 +5633,10 @@
       <x:c r="J158" s="44" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="K158" s="45" t="n">
+      <x:c r="K158" s="44" t="n">
         <x:v>142565</x:v>
       </x:c>
+      <x:c r="L158" s="57" t="str"/>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="46" t="str">
@@ -5493,9 +5665,10 @@
       <x:c r="J159" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K159" s="50" t="n">
+      <x:c r="K159" s="49" t="n">
         <x:v>1918</x:v>
       </x:c>
+      <x:c r="L159" s="58" t="str"/>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="46" t="str">
@@ -5524,9 +5697,10 @@
       <x:c r="J160" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K160" s="50" t="n">
+      <x:c r="K160" s="49" t="n">
         <x:v>4891</x:v>
       </x:c>
+      <x:c r="L160" s="58" t="str"/>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="46" t="str">
@@ -5555,9 +5729,10 @@
       <x:c r="J161" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K161" s="50" t="n">
+      <x:c r="K161" s="49" t="n">
         <x:v>11257</x:v>
       </x:c>
+      <x:c r="L161" s="58" t="str"/>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="46" t="str">
@@ -5586,9 +5761,10 @@
       <x:c r="J162" s="49" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="K162" s="50" t="n">
+      <x:c r="K162" s="49" t="n">
         <x:v>12982</x:v>
       </x:c>
+      <x:c r="L162" s="58" t="str"/>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="46" t="str">
@@ -5617,9 +5793,10 @@
       <x:c r="J163" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K163" s="50" t="n">
+      <x:c r="K163" s="49" t="n">
         <x:v>3692</x:v>
       </x:c>
+      <x:c r="L163" s="58" t="str"/>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="46" t="str">
@@ -5648,9 +5825,10 @@
       <x:c r="J164" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K164" s="50" t="n">
+      <x:c r="K164" s="49" t="n">
         <x:v>976</x:v>
       </x:c>
+      <x:c r="L164" s="58" t="str"/>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="46" t="str">
@@ -5679,9 +5857,10 @@
       <x:c r="J165" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K165" s="50" t="n">
+      <x:c r="K165" s="49" t="n">
         <x:v>3616</x:v>
       </x:c>
+      <x:c r="L165" s="58" t="str"/>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="46" t="str">
@@ -5710,9 +5889,10 @@
       <x:c r="J166" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K166" s="50" t="n">
+      <x:c r="K166" s="49" t="n">
         <x:v>5193</x:v>
       </x:c>
+      <x:c r="L166" s="58" t="str"/>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="46" t="str">
@@ -5741,9 +5921,10 @@
       <x:c r="J167" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K167" s="50" t="n">
+      <x:c r="K167" s="49" t="n">
         <x:v>3119</x:v>
       </x:c>
+      <x:c r="L167" s="58" t="str"/>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="46" t="str">
@@ -5772,9 +5953,10 @@
       <x:c r="J168" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K168" s="50" t="n">
+      <x:c r="K168" s="49" t="n">
         <x:v>19464</x:v>
       </x:c>
+      <x:c r="L168" s="58" t="str"/>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="46" t="str">
@@ -5803,9 +5985,10 @@
       <x:c r="J169" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K169" s="50" t="n">
+      <x:c r="K169" s="49" t="n">
         <x:v>5112</x:v>
       </x:c>
+      <x:c r="L169" s="58" t="str"/>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="46" t="str">
@@ -5834,9 +6017,10 @@
       <x:c r="J170" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K170" s="50" t="n">
+      <x:c r="K170" s="49" t="n">
         <x:v>2121</x:v>
       </x:c>
+      <x:c r="L170" s="58" t="str"/>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="46" t="str">
@@ -5865,9 +6049,10 @@
       <x:c r="J171" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K171" s="50" t="n">
+      <x:c r="K171" s="49" t="n">
         <x:v>2675</x:v>
       </x:c>
+      <x:c r="L171" s="58" t="str"/>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="46" t="str">
@@ -5896,9 +6081,10 @@
       <x:c r="J172" s="49" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K172" s="50" t="n">
+      <x:c r="K172" s="49" t="n">
         <x:v>5390</x:v>
       </x:c>
+      <x:c r="L172" s="58" t="str"/>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="46" t="str">
@@ -5927,9 +6113,10 @@
       <x:c r="J173" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K173" s="50" t="n">
+      <x:c r="K173" s="49" t="n">
         <x:v>3201</x:v>
       </x:c>
+      <x:c r="L173" s="58" t="str"/>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="46" t="str">
@@ -5958,9 +6145,10 @@
       <x:c r="J174" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K174" s="50" t="n">
+      <x:c r="K174" s="49" t="n">
         <x:v>34647</x:v>
       </x:c>
+      <x:c r="L174" s="58" t="str"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="46" t="str">
@@ -5989,9 +6177,10 @@
       <x:c r="J175" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K175" s="50" t="n">
+      <x:c r="K175" s="49" t="n">
         <x:v>1542</x:v>
       </x:c>
+      <x:c r="L175" s="58" t="str"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="46" t="str">
@@ -6020,9 +6209,10 @@
       <x:c r="J176" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K176" s="50" t="n">
+      <x:c r="K176" s="49" t="n">
         <x:v>3831</x:v>
       </x:c>
+      <x:c r="L176" s="58" t="str"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="46" t="str">
@@ -6051,9 +6241,10 @@
       <x:c r="J177" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K177" s="50" t="n">
+      <x:c r="K177" s="49" t="n">
         <x:v>2680</x:v>
       </x:c>
+      <x:c r="L177" s="58" t="str"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="46" t="str">
@@ -6082,9 +6273,10 @@
       <x:c r="J178" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K178" s="50" t="n">
+      <x:c r="K178" s="49" t="n">
         <x:v>3562</x:v>
       </x:c>
+      <x:c r="L178" s="58" t="str"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="46" t="str">
@@ -6113,9 +6305,10 @@
       <x:c r="J179" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K179" s="50" t="n">
+      <x:c r="K179" s="49" t="n">
         <x:v>3710</x:v>
       </x:c>
+      <x:c r="L179" s="58" t="str"/>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="46" t="str">
@@ -6144,9 +6337,10 @@
       <x:c r="J180" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K180" s="50" t="n">
+      <x:c r="K180" s="49" t="n">
         <x:v>6986</x:v>
       </x:c>
+      <x:c r="L180" s="58" t="str"/>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="41" t="str">
@@ -6171,9 +6365,10 @@
       <x:c r="J181" s="44" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="K181" s="45" t="n">
+      <x:c r="K181" s="44" t="n">
         <x:v>5156</x:v>
       </x:c>
+      <x:c r="L181" s="57" t="str"/>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="46" t="str">
@@ -6202,9 +6397,10 @@
       <x:c r="J182" s="49" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K182" s="50" t="n">
+      <x:c r="K182" s="49" t="n">
         <x:v>753</x:v>
       </x:c>
+      <x:c r="L182" s="58" t="str"/>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="46" t="str">
@@ -6233,9 +6429,10 @@
       <x:c r="J183" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K183" s="50" t="n">
+      <x:c r="K183" s="49" t="n">
         <x:v>120</x:v>
       </x:c>
+      <x:c r="L183" s="58" t="str"/>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="46" t="str">
@@ -6264,9 +6461,10 @@
       <x:c r="J184" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K184" s="50" t="n">
+      <x:c r="K184" s="49" t="n">
         <x:v>257</x:v>
       </x:c>
+      <x:c r="L184" s="58" t="str"/>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="46" t="str">
@@ -6291,9 +6489,10 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J185" s="49"/>
-      <x:c r="K185" s="50" t="n">
+      <x:c r="K185" s="49" t="n">
         <x:v>66</x:v>
       </x:c>
+      <x:c r="L185" s="58" t="str"/>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="46" t="str">
@@ -6322,9 +6521,10 @@
       <x:c r="J186" s="49" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K186" s="50" t="n">
+      <x:c r="K186" s="49" t="n">
         <x:v>1719</x:v>
       </x:c>
+      <x:c r="L186" s="58" t="str"/>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="46" t="str">
@@ -6353,9 +6553,10 @@
       <x:c r="J187" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K187" s="50" t="n">
+      <x:c r="K187" s="49" t="n">
         <x:v>52</x:v>
       </x:c>
+      <x:c r="L187" s="58" t="str"/>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="46" t="str">
@@ -6384,9 +6585,10 @@
       <x:c r="J188" s="49" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K188" s="50" t="n">
+      <x:c r="K188" s="49" t="n">
         <x:v>732</x:v>
       </x:c>
+      <x:c r="L188" s="58" t="str"/>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="46" t="str">
@@ -6415,9 +6617,10 @@
       <x:c r="J189" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K189" s="50" t="n">
+      <x:c r="K189" s="49" t="n">
         <x:v>96</x:v>
       </x:c>
+      <x:c r="L189" s="58" t="str"/>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="46" t="str">
@@ -6446,9 +6649,10 @@
       <x:c r="J190" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K190" s="50" t="n">
+      <x:c r="K190" s="49" t="n">
         <x:v>335</x:v>
       </x:c>
+      <x:c r="L190" s="58" t="str"/>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="46" t="str">
@@ -6473,7 +6677,8 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J191" s="49"/>
-      <x:c r="K191" s="50"/>
+      <x:c r="K191" s="49"/>
+      <x:c r="L191" s="58" t="str"/>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="46" t="str">
@@ -6502,9 +6707,10 @@
       <x:c r="J192" s="49" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K192" s="50" t="n">
+      <x:c r="K192" s="49" t="n">
         <x:v>936</x:v>
       </x:c>
+      <x:c r="L192" s="58" t="str"/>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="46" t="str">
@@ -6533,9 +6739,10 @@
       <x:c r="J193" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K193" s="50" t="n">
+      <x:c r="K193" s="49" t="n">
         <x:v>121</x:v>
       </x:c>
+      <x:c r="L193" s="58" t="str"/>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="46" t="str">
@@ -6564,9 +6771,10 @@
       <x:c r="J194" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K194" s="50" t="n">
+      <x:c r="K194" s="49" t="n">
         <x:v>35</x:v>
       </x:c>
+      <x:c r="L194" s="58" t="str"/>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="41" t="str">
@@ -6591,9 +6799,10 @@
       <x:c r="J195" s="44" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="K195" s="45" t="n">
+      <x:c r="K195" s="44" t="n">
         <x:v>4880</x:v>
       </x:c>
+      <x:c r="L195" s="57" t="str"/>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="46" t="str">
@@ -6622,9 +6831,10 @@
       <x:c r="J196" s="49" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K196" s="50" t="n">
+      <x:c r="K196" s="49" t="n">
         <x:v>765</x:v>
       </x:c>
+      <x:c r="L196" s="58" t="str"/>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="46" t="str">
@@ -6653,9 +6863,10 @@
       <x:c r="J197" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K197" s="50" t="n">
+      <x:c r="K197" s="49" t="n">
         <x:v>114</x:v>
       </x:c>
+      <x:c r="L197" s="58" t="str"/>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="46" t="str">
@@ -6684,9 +6895,10 @@
       <x:c r="J198" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K198" s="50" t="n">
+      <x:c r="K198" s="49" t="n">
         <x:v>265</x:v>
       </x:c>
+      <x:c r="L198" s="58" t="str"/>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="46" t="str">
@@ -6715,9 +6927,10 @@
       <x:c r="J199" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K199" s="50" t="n">
+      <x:c r="K199" s="49" t="n">
         <x:v>118</x:v>
       </x:c>
+      <x:c r="L199" s="58" t="str"/>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="46" t="str">
@@ -6746,9 +6959,10 @@
       <x:c r="J200" s="49" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="K200" s="50" t="n">
+      <x:c r="K200" s="49" t="n">
         <x:v>3618</x:v>
       </x:c>
+      <x:c r="L200" s="58" t="str"/>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="41" t="str">
@@ -6773,9 +6987,10 @@
       <x:c r="J201" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K201" s="45" t="n">
+      <x:c r="K201" s="44" t="n">
         <x:v>14036</x:v>
       </x:c>
+      <x:c r="L201" s="57" t="str"/>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="46" t="str">
@@ -6804,9 +7019,10 @@
       <x:c r="J202" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K202" s="50" t="n">
+      <x:c r="K202" s="49" t="n">
         <x:v>46</x:v>
       </x:c>
+      <x:c r="L202" s="58" t="str"/>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="46" t="str">
@@ -6835,9 +7051,10 @@
       <x:c r="J203" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K203" s="50" t="n">
+      <x:c r="K203" s="49" t="n">
         <x:v>6748</x:v>
       </x:c>
+      <x:c r="L203" s="58" t="str"/>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="46" t="str">
@@ -6866,9 +7083,10 @@
       <x:c r="J204" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K204" s="50" t="n">
+      <x:c r="K204" s="49" t="n">
         <x:v>5867</x:v>
       </x:c>
+      <x:c r="L204" s="58" t="str"/>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="46" t="str">
@@ -6897,9 +7115,10 @@
       <x:c r="J205" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K205" s="50" t="n">
+      <x:c r="K205" s="49" t="n">
         <x:v>1375</x:v>
       </x:c>
+      <x:c r="L205" s="58" t="str"/>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="41" t="str">
@@ -6924,9 +7143,10 @@
       <x:c r="J206" s="44" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="K206" s="45" t="n">
+      <x:c r="K206" s="44" t="n">
         <x:v>4265</x:v>
       </x:c>
+      <x:c r="L206" s="57" t="str"/>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="46" t="str">
@@ -6955,9 +7175,10 @@
       <x:c r="J207" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K207" s="50" t="n">
+      <x:c r="K207" s="49" t="n">
         <x:v>87</x:v>
       </x:c>
+      <x:c r="L207" s="58" t="str"/>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="46" t="str">
@@ -6986,9 +7207,10 @@
       <x:c r="J208" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K208" s="50" t="n">
+      <x:c r="K208" s="49" t="n">
         <x:v>294</x:v>
       </x:c>
+      <x:c r="L208" s="58" t="str"/>
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="46" t="str">
@@ -7017,9 +7239,10 @@
       <x:c r="J209" s="49" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="K209" s="50" t="n">
+      <x:c r="K209" s="49" t="n">
         <x:v>3788</x:v>
       </x:c>
+      <x:c r="L209" s="58" t="str"/>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="46" t="str">
@@ -7048,9 +7271,10 @@
       <x:c r="J210" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K210" s="50" t="n">
+      <x:c r="K210" s="49" t="n">
         <x:v>96</x:v>
       </x:c>
+      <x:c r="L210" s="58" t="str"/>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="41" t="str">
@@ -7075,9 +7299,10 @@
       <x:c r="J211" s="44" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K211" s="45" t="n">
+      <x:c r="K211" s="44" t="n">
         <x:v>99825</x:v>
       </x:c>
+      <x:c r="L211" s="57" t="str"/>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="46" t="str">
@@ -7106,9 +7331,10 @@
       <x:c r="J212" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K212" s="50" t="n">
+      <x:c r="K212" s="49" t="n">
         <x:v>3435</x:v>
       </x:c>
+      <x:c r="L212" s="58" t="str"/>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="46" t="str">
@@ -7137,9 +7363,10 @@
       <x:c r="J213" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K213" s="50" t="n">
+      <x:c r="K213" s="49" t="n">
         <x:v>84993</x:v>
       </x:c>
+      <x:c r="L213" s="58" t="str"/>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="46" t="str">
@@ -7168,9 +7395,10 @@
       <x:c r="J214" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K214" s="50" t="n">
+      <x:c r="K214" s="49" t="n">
         <x:v>1300</x:v>
       </x:c>
+      <x:c r="L214" s="58" t="str"/>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="46" t="str">
@@ -7199,9 +7427,10 @@
       <x:c r="J215" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K215" s="50" t="n">
+      <x:c r="K215" s="49" t="n">
         <x:v>765</x:v>
       </x:c>
+      <x:c r="L215" s="58" t="str"/>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="46" t="str">
@@ -7230,9 +7459,10 @@
       <x:c r="J216" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K216" s="50" t="n">
+      <x:c r="K216" s="49" t="n">
         <x:v>2602</x:v>
       </x:c>
+      <x:c r="L216" s="58" t="str"/>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="46" t="str">
@@ -7261,9 +7491,10 @@
       <x:c r="J217" s="49" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K217" s="50" t="n">
+      <x:c r="K217" s="49" t="n">
         <x:v>2038</x:v>
       </x:c>
+      <x:c r="L217" s="58" t="str"/>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="46" t="str">
@@ -7292,9 +7523,10 @@
       <x:c r="J218" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K218" s="50" t="n">
+      <x:c r="K218" s="49" t="n">
         <x:v>2489</x:v>
       </x:c>
+      <x:c r="L218" s="58" t="str"/>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="46" t="str">
@@ -7323,9 +7555,10 @@
       <x:c r="J219" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K219" s="50" t="n">
+      <x:c r="K219" s="49" t="n">
         <x:v>2203</x:v>
       </x:c>
+      <x:c r="L219" s="58" t="str"/>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="41" t="str">
@@ -7350,9 +7583,10 @@
       <x:c r="J220" s="44" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K220" s="45" t="n">
+      <x:c r="K220" s="44" t="n">
         <x:v>13531</x:v>
       </x:c>
+      <x:c r="L220" s="57" t="str"/>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="46" t="str">
@@ -7381,9 +7615,10 @@
       <x:c r="J221" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K221" s="50" t="n">
+      <x:c r="K221" s="49" t="n">
         <x:v>4658</x:v>
       </x:c>
+      <x:c r="L221" s="58" t="str"/>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="46" t="str">
@@ -7412,9 +7647,10 @@
       <x:c r="J222" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K222" s="50" t="n">
+      <x:c r="K222" s="49" t="n">
         <x:v>2510</x:v>
       </x:c>
+      <x:c r="L222" s="58" t="str"/>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="46" t="str">
@@ -7443,9 +7679,10 @@
       <x:c r="J223" s="49" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K223" s="50" t="n">
+      <x:c r="K223" s="49" t="n">
         <x:v>6363</x:v>
       </x:c>
+      <x:c r="L223" s="58" t="str"/>
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="41" t="str">
@@ -7470,9 +7707,10 @@
       <x:c r="J224" s="44" t="n">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="K224" s="45" t="n">
+      <x:c r="K224" s="44" t="n">
         <x:v>45911</x:v>
       </x:c>
+      <x:c r="L224" s="57" t="str"/>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="46" t="str">
@@ -7501,9 +7739,10 @@
       <x:c r="J225" s="49" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K225" s="50" t="n">
+      <x:c r="K225" s="49" t="n">
         <x:v>6086</x:v>
       </x:c>
+      <x:c r="L225" s="58" t="str"/>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="46" t="str">
@@ -7532,9 +7771,10 @@
       <x:c r="J226" s="49" t="n">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="K226" s="50" t="n">
+      <x:c r="K226" s="49" t="n">
         <x:v>39825</x:v>
       </x:c>
+      <x:c r="L226" s="58" t="str"/>
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="41" t="str">
@@ -7559,9 +7799,10 @@
       <x:c r="J227" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K227" s="45" t="n">
+      <x:c r="K227" s="44" t="n">
         <x:v>23588</x:v>
       </x:c>
+      <x:c r="L227" s="57" t="str"/>
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="46" t="str">
@@ -7590,9 +7831,10 @@
       <x:c r="J228" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K228" s="50" t="n">
+      <x:c r="K228" s="49" t="n">
         <x:v>483</x:v>
       </x:c>
+      <x:c r="L228" s="58" t="str"/>
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="46" t="str">
@@ -7621,9 +7863,10 @@
       <x:c r="J229" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K229" s="50" t="n">
+      <x:c r="K229" s="49" t="n">
         <x:v>509</x:v>
       </x:c>
+      <x:c r="L229" s="58" t="str"/>
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="46" t="str">
@@ -7652,9 +7895,10 @@
       <x:c r="J230" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K230" s="50" t="n">
+      <x:c r="K230" s="49" t="n">
         <x:v>359</x:v>
       </x:c>
+      <x:c r="L230" s="58" t="str"/>
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="46" t="str">
@@ -7683,9 +7927,10 @@
       <x:c r="J231" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K231" s="50" t="n">
+      <x:c r="K231" s="49" t="n">
         <x:v>15381</x:v>
       </x:c>
+      <x:c r="L231" s="58" t="str"/>
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="46" t="str">
@@ -7710,9 +7955,10 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J232" s="49"/>
-      <x:c r="K232" s="50" t="n">
+      <x:c r="K232" s="49" t="n">
         <x:v>232</x:v>
       </x:c>
+      <x:c r="L232" s="58" t="str"/>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="46" t="str">
@@ -7741,9 +7987,10 @@
       <x:c r="J233" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K233" s="50" t="n">
+      <x:c r="K233" s="49" t="n">
         <x:v>6856</x:v>
       </x:c>
+      <x:c r="L233" s="58" t="str"/>
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="46" t="str">
@@ -7768,9 +8015,10 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J234" s="49"/>
-      <x:c r="K234" s="50" t="n">
+      <x:c r="K234" s="49" t="n">
         <x:v>237</x:v>
       </x:c>
+      <x:c r="L234" s="58" t="str"/>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="41" t="str">
@@ -7795,9 +8043,10 @@
       <x:c r="J235" s="44" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K235" s="45" t="n">
+      <x:c r="K235" s="44" t="n">
         <x:v>13584</x:v>
       </x:c>
+      <x:c r="L235" s="57" t="str"/>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="46" t="str">
@@ -7826,9 +8075,10 @@
       <x:c r="J236" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K236" s="50" t="n">
+      <x:c r="K236" s="49" t="n">
         <x:v>10224</x:v>
       </x:c>
+      <x:c r="L236" s="58" t="str"/>
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="46" t="str">
@@ -7857,9 +8107,10 @@
       <x:c r="J237" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K237" s="50" t="n">
+      <x:c r="K237" s="49" t="n">
         <x:v>744</x:v>
       </x:c>
+      <x:c r="L237" s="58" t="str"/>
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="46" t="str">
@@ -7884,9 +8135,10 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J238" s="49"/>
-      <x:c r="K238" s="50" t="n">
+      <x:c r="K238" s="49" t="n">
         <x:v>233</x:v>
       </x:c>
+      <x:c r="L238" s="58" t="str"/>
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="46" t="str">
@@ -7911,9 +8163,10 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J239" s="49"/>
-      <x:c r="K239" s="50" t="n">
+      <x:c r="K239" s="49" t="n">
         <x:v>145</x:v>
       </x:c>
+      <x:c r="L239" s="58" t="str"/>
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="46" t="str">
@@ -7942,9 +8195,10 @@
       <x:c r="J240" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K240" s="50" t="n">
+      <x:c r="K240" s="49" t="n">
         <x:v>151</x:v>
       </x:c>
+      <x:c r="L240" s="58" t="str"/>
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="46" t="str">
@@ -7973,9 +8227,10 @@
       <x:c r="J241" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K241" s="50" t="n">
+      <x:c r="K241" s="49" t="n">
         <x:v>391</x:v>
       </x:c>
+      <x:c r="L241" s="58" t="str"/>
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="46" t="str">
@@ -8004,9 +8259,10 @@
       <x:c r="J242" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K242" s="50" t="n">
+      <x:c r="K242" s="49" t="n">
         <x:v>1899</x:v>
       </x:c>
+      <x:c r="L242" s="58" t="str"/>
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="46" t="str">
@@ -8031,9 +8287,10 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J243" s="49"/>
-      <x:c r="K243" s="50" t="n">
+      <x:c r="K243" s="49" t="n">
         <x:v>505</x:v>
       </x:c>
+      <x:c r="L243" s="58" t="str"/>
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="46" t="str">
@@ -8062,9 +8319,10 @@
       <x:c r="J244" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K244" s="50" t="n">
+      <x:c r="K244" s="49" t="n">
         <x:v>175</x:v>
       </x:c>
+      <x:c r="L244" s="58" t="str"/>
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="41" t="str">
@@ -8089,9 +8347,10 @@
       <x:c r="J245" s="44" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="K245" s="45" t="n">
+      <x:c r="K245" s="44" t="n">
         <x:v>4877</x:v>
       </x:c>
+      <x:c r="L245" s="57" t="str"/>
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="46" t="str">
@@ -8120,9 +8379,10 @@
       <x:c r="J246" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K246" s="50" t="n">
+      <x:c r="K246" s="49" t="n">
         <x:v>221</x:v>
       </x:c>
+      <x:c r="L246" s="58" t="str"/>
     </x:row>
     <x:row r="247">
       <x:c r="A247" s="46" t="str">
@@ -8151,9 +8411,10 @@
       <x:c r="J247" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K247" s="50" t="n">
+      <x:c r="K247" s="49" t="n">
         <x:v>436</x:v>
       </x:c>
+      <x:c r="L247" s="58" t="str"/>
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="46" t="str">
@@ -8182,9 +8443,10 @@
       <x:c r="J248" s="49" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K248" s="50" t="n">
+      <x:c r="K248" s="49" t="n">
         <x:v>712</x:v>
       </x:c>
+      <x:c r="L248" s="58" t="str"/>
     </x:row>
     <x:row r="249">
       <x:c r="A249" s="46" t="str">
@@ -8213,9 +8475,10 @@
       <x:c r="J249" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K249" s="50" t="n">
+      <x:c r="K249" s="49" t="n">
         <x:v>358</x:v>
       </x:c>
+      <x:c r="L249" s="58" t="str"/>
     </x:row>
     <x:row r="250">
       <x:c r="A250" s="46" t="str">
@@ -8244,9 +8507,10 @@
       <x:c r="J250" s="49" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K250" s="50" t="n">
+      <x:c r="K250" s="49" t="n">
         <x:v>221</x:v>
       </x:c>
+      <x:c r="L250" s="58" t="str"/>
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="46" t="str">
@@ -8275,9 +8539,10 @@
       <x:c r="J251" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K251" s="50" t="n">
+      <x:c r="K251" s="49" t="n">
         <x:v>149</x:v>
       </x:c>
+      <x:c r="L251" s="58" t="str"/>
     </x:row>
     <x:row r="252">
       <x:c r="A252" s="46" t="str">
@@ -8306,9 +8571,10 @@
       <x:c r="J252" s="49" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K252" s="50" t="n">
+      <x:c r="K252" s="49" t="n">
         <x:v>87</x:v>
       </x:c>
+      <x:c r="L252" s="58" t="str"/>
     </x:row>
     <x:row r="253">
       <x:c r="A253" s="46" t="str">
@@ -8337,9 +8603,10 @@
       <x:c r="J253" s="49" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="K253" s="50" t="n">
+      <x:c r="K253" s="49" t="n">
         <x:v>1117</x:v>
       </x:c>
+      <x:c r="L253" s="58" t="str"/>
     </x:row>
     <x:row r="254">
       <x:c r="A254" s="46" t="str">
@@ -8368,9 +8635,10 @@
       <x:c r="J254" s="49" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="K254" s="50" t="n">
+      <x:c r="K254" s="49" t="n">
         <x:v>1576</x:v>
       </x:c>
+      <x:c r="L254" s="58" t="str"/>
     </x:row>
     <x:row r="255">
       <x:c r="A255" s="41" t="str">
@@ -8391,7 +8659,8 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J255" s="44"/>
-      <x:c r="K255" s="45"/>
+      <x:c r="K255" s="44"/>
+      <x:c r="L255" s="57" t="str"/>
     </x:row>
     <x:row r="256">
       <x:c r="A256" s="51" t="str">
@@ -8416,12 +8685,13 @@
         <x:v>sin_dato</x:v>
       </x:c>
       <x:c r="J256" s="54"/>
-      <x:c r="K256" s="55"/>
+      <x:c r="K256" s="54"/>
+      <x:c r="L256" s="59" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:K2"/>
-    <x:mergeCell ref="A3:K3"/>
+    <x:mergeCell ref="A1:L2"/>
+    <x:mergeCell ref="A3:L3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
